--- a/exports/494_apalla-calabaza.xlsx
+++ b/exports/494_apalla-calabaza.xlsx
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>74276222</t>
+          <t>91305256</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AZAÑERO</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CORNEJO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SUMMER MANUEL</t>
+          <t>ISAAC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,16 +2337,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13/12/1998</t>
+          <t>27/04/2019</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>91305256</t>
+          <t>42007257</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>BORQUEZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORNEJO</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ISAAC</t>
+          <t>EVARISTO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27/04/2019</t>
+          <t>26/10/1981</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42007257</t>
+          <t>45541017</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>TUPALAYA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EVARISTO</t>
+          <t>MARINA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26/10/1981</t>
+          <t>16/07/1973</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,35 +2502,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45541017</t>
+          <t>44308999</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BORQUEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TUPALAYA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARINA</t>
+          <t>OLIVIO OSCAR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>16/07/1973</t>
+          <t>06/12/1986</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44308999</t>
+          <t>47537676</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OLIVIO OSCAR</t>
+          <t>JESUS DE NASARET</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/12/1986</t>
+          <t>28/05/1990</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,40 +2628,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>47537676</t>
+          <t>76940884</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>CAIRAMPOMA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESUS DE NASARET</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28/05/1990</t>
+          <t>15/05/1999</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2691,45 +2691,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>76940884</t>
+          <t>60366731</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAIRAMPOMA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t>JHAMPOL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15/05/1999</t>
+          <t>26/03/2009</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>60366731</t>
+          <t>48214604</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,35 +2764,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JHAMPOL</t>
+          <t>ADA VELINDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>26/03/2009</t>
+          <t>18/12/1992</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>48214604</t>
+          <t>80074302</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAMARENA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ADA VELINDA</t>
+          <t>BRIGIDA OLINDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/12/1992</t>
+          <t>14/04/1977</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>80074302</t>
+          <t>41789336</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,20 +2895,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BRIGIDA OLINDA</t>
+          <t>WALTER ROLANDO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14/04/1977</t>
+          <t>05/05/1980</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41789336</t>
+          <t>73385444</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WALTER ROLANDO</t>
+          <t>URBANO PERCILES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/05/1980</t>
+          <t>10/05/1996</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>21/12/2011</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>73385444</t>
+          <t>60552816</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMARENA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>URBANO PERCILES</t>
+          <t>MAYDA SAYURI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10/05/1996</t>
+          <t>24/10/2007</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21/12/2011</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>60552816</t>
+          <t>20118276</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAYDA SAYURI</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24/10/2007</t>
+          <t>02/06/1978</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>06/12/2012</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,22 +3132,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20118276</t>
+          <t>92123570</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ELENA</t>
+          <t>YOVITSA YANINA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02/06/1978</t>
+          <t>07/08/2020</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06/12/2012</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,45 +3195,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>92123570</t>
+          <t>20964970</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>YOVITSA YANINA</t>
+          <t>SEBASTIAN MAURO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>07/08/2020</t>
+          <t>20/01/1962</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20964970</t>
+          <t>75847551</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SEBASTIAN MAURO</t>
+          <t>FRAN SAUL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20/01/1962</t>
+          <t>05/03/1999</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>75847551</t>
+          <t>63421050</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GALAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FRAN SAUL</t>
+          <t>JOSELO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/03/1999</t>
+          <t>06/01/2012</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/05/2013</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>63421050</t>
+          <t>92106434</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GALAN</t>
+          <t>YOMPIRI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JOSELO</t>
+          <t>JAIRO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>06/01/2012</t>
+          <t>12/11/2020</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09/05/2013</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>92106434</t>
+          <t>40867686</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YOMPIRI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JAIRO</t>
+          <t>ROQUE JUVENAL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12/11/2020</t>
+          <t>03/05/1981</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,22 +3510,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>40867686</t>
+          <t>23682758</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>CLEMENTE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>CASTRO</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HUAMAN</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ROQUE JUVENAL</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>03/05/1981</t>
+          <t>27/03/1972</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23682758</t>
+          <t>92373689</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>DAMACIO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>YORAM HEYCOB</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>27/03/1972</t>
+          <t>24/05/2021</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,40 +3636,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>92373689</t>
+          <t>21006143</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DAMACIO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DE PARIONA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>YORAM HEYCOB</t>
+          <t>GREGORIA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/05/2021</t>
+          <t>09/05/1955</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21006143</t>
+          <t>76566154</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,30 +3709,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE PARIONA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GREGORIA</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>09/05/1955</t>
+          <t>15/01/1995</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>26/10/2017</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>76566154</t>
+          <t>75875224</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>BRANDO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>15/01/1995</t>
+          <t>26/11/2001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>26/10/2017</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>75875224</t>
+          <t>75875226</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BRANDO</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3849,11 +3849,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>26/11/2001</t>
+          <t>17/06/2004</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>75875226</t>
+          <t>20416766</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>CESARIO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2004</t>
+          <t>01/11/1967</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20416766</t>
+          <t>75875221</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CESARIO</t>
+          <t>FILCLINTON BRAYAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01/11/1967</t>
+          <t>14/11/1998</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>75875221</t>
+          <t>63260158</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FILCLINTON BRAYAN</t>
+          <t>ROLANDO JHONY</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,11 +4038,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14/11/1998</t>
+          <t>15/04/2007</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>63260158</t>
+          <t>49024751</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,35 +4087,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ROLANDO JHONY</t>
+          <t>GEOVANA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15/04/2007</t>
+          <t>15/02/1992</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>09/09/2019</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,35 +4140,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>49024751</t>
+          <t>48975659</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GEOVANA</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15/02/1992</t>
+          <t>12/10/1982</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>09/09/2019</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>48975659</t>
+          <t>23685653</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4213,35 +4213,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>DE CHAHUA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12/10/1982</t>
+          <t>11/02/1951</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,45 +4266,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>23685653</t>
+          <t>20993630</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GAGO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE CHAHUA</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11/02/1951</t>
+          <t>14/03/1970</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,35 +4329,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20993630</t>
+          <t>21012969</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GAGO</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>FLORA FELICITA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14/03/1970</t>
+          <t>02/05/1977</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21012969</t>
+          <t>73715248</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4407,20 +4407,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FLORA FELICITA</t>
+          <t>ROY WILSON</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02/05/1977</t>
+          <t>09/05/1995</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>08/12/2011</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>73715248</t>
+          <t>61452157</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ROY WILSON</t>
+          <t>HILARI MILEYDI</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/05/1995</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>08/12/2011</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>61452157</t>
+          <t>72579431</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4528,35 +4528,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HILARI MILEYDI</t>
+          <t>ISAI ALEJANDRO</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>19/01/1996</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>72579431</t>
+          <t>20988579</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ISAI ALEJANDRO</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,16 +4605,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/01/1996</t>
+          <t>26/05/1957</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20988579</t>
+          <t>74940517</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GONZALO</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>YOLINDA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>26/05/1957</t>
+          <t>10/02/1997</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>74940517</t>
+          <t>73446305</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>HUARI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>YOLINDA</t>
+          <t>BRANDUM MAIK</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10/02/1997</t>
+          <t>01/09/1996</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,45 +4770,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>73446305</t>
+          <t>93836589</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUARI</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BRANDUM MAIK</t>
+          <t>ABEGAIL REYNA VALERIA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01/09/1996</t>
+          <t>07/03/2024</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>93836589</t>
+          <t>21002974</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ABEGAIL REYNA VALERIA</t>
+          <t>JULIA PRIMITIVA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>07/03/2024</t>
+          <t>16/09/1975</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>21002974</t>
+          <t>75753510</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JULIA PRIMITIVA</t>
+          <t>DIANA YULISA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>16/09/1975</t>
+          <t>28/12/1999</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>75753510</t>
+          <t>47269907</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4969,30 +4969,30 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DIANA YULISA</t>
+          <t>EDINSON</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>28/12/1999</t>
+          <t>09/09/1992</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>47269907</t>
+          <t>92204627</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EDINSON</t>
+          <t>SARAI ABIGAIL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>09/09/1992</t>
+          <t>30/04/2020</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,7 +5085,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>92204627</t>
+          <t>20997750</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5095,35 +5095,35 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SARAI ABIGAIL</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>30/04/2020</t>
+          <t>12/03/1970</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,17 +5148,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20997750</t>
+          <t>45474660</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5172,11 +5172,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12/03/1970</t>
+          <t>08/01/1986</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>15/11/2012</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>45474660</t>
+          <t>20991283</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>JULCARIMA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>VICENTE HERMOGENES</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>08/01/1986</t>
+          <t>19/04/1967</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>15/11/2012</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,35 +5274,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20991283</t>
+          <t>40153216</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JULCARIMA</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>BARTOLO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VICENTE HERMOGENES</t>
+          <t>YOVANA DORINA</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/04/1967</t>
+          <t>12/04/1979</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>40153216</t>
+          <t>73092414</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5347,30 +5347,30 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BARTOLO</t>
+          <t>CERRON</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>YOVANA DORINA</t>
+          <t>YAYIR HUMBERTO</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12/04/1979</t>
+          <t>21/11/1999</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>73092414</t>
+          <t>61618592</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CERRON</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>YAYIR HUMBERTO</t>
+          <t>LEONEL SMIT</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21/11/1999</t>
+          <t>12/12/1999</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,22 +5463,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>61618592</t>
+          <t>21003014</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEONEL SMIT</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5487,21 +5487,21 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12/12/1999</t>
+          <t>13/11/1944</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21003014</t>
+          <t>21003908</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,11 +5550,11 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13/11/1944</t>
+          <t>28/11/1963</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21003908</t>
+          <t>20411532</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>DOMINGO</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/11/1963</t>
+          <t>15/06/1947</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20411532</t>
+          <t>48622054</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5662,30 +5662,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DOMINGO</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>15/06/1947</t>
+          <t>19/01/1995</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>08/06/2015</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>48622054</t>
+          <t>75875229</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5730,25 +5730,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>CHARLYS ORLANDO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19/01/1995</t>
+          <t>15/10/2001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>08/06/2015</t>
+          <t>26/03/2018</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>75875229</t>
+          <t>75875228</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CHARLYS ORLANDO</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>15/10/2001</t>
+          <t>14/10/2003</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5841,7 +5841,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>75875228</t>
+          <t>81417430</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5856,25 +5856,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>SULLY JAZMIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14/10/2003</t>
+          <t>16/06/2014</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>26/03/2018</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>81417430</t>
+          <t>44314926</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SULLY JAZMIN</t>
+          <t>CELIA CARMEN</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16/06/2014</t>
+          <t>03/06/1987</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>44314926</t>
+          <t>47262412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5977,25 +5977,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CELIA CARMEN</t>
+          <t>ABELANGE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>03/06/1987</t>
+          <t>04/02/1992</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>47262412</t>
+          <t>21011849</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ABELANGE</t>
+          <t>GERONIMO EMILIANO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/02/1992</t>
+          <t>20/07/1958</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,40 +6093,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21011849</t>
+          <t>41755830</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GERONIMO EMILIANO</t>
+          <t>IRENE MARILU</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20/07/1958</t>
+          <t>24/03/1983</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">

--- a/exports/494_apalla-calabaza.xlsx
+++ b/exports/494_apalla-calabaza.xlsx
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>91305256</t>
+          <t>74276222</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>AZAÑERO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CORNEJO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ISAAC</t>
+          <t>SUMMER MANUEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,16 +2337,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>27/04/2019</t>
+          <t>13/12/1998</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42007257</t>
+          <t>91305256</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BORQUEZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>CORNEJO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EVARISTO</t>
+          <t>ISAAC</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>26/10/1981</t>
+          <t>27/04/2019</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>45541017</t>
+          <t>42007257</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TUPALAYA</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MARINA</t>
+          <t>EVARISTO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>16/07/1973</t>
+          <t>26/10/1981</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,35 +2502,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>44308999</t>
+          <t>45541017</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>BORQUEZ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>TUPALAYA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OLIVIO OSCAR</t>
+          <t>MARINA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/12/1986</t>
+          <t>16/07/1973</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>47537676</t>
+          <t>44308999</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JESUS DE NASARET</t>
+          <t>OLIVIO OSCAR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28/05/1990</t>
+          <t>06/12/1986</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,40 +2628,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>76940884</t>
+          <t>47537676</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAIRAMPOMA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t>JESUS DE NASARET</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15/05/1999</t>
+          <t>28/05/1990</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2691,45 +2691,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>60366731</t>
+          <t>76940884</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAIRAMPOMA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JHAMPOL</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>26/03/2009</t>
+          <t>15/05/1999</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>48214604</t>
+          <t>60366731</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,35 +2764,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADA VELINDA</t>
+          <t>JHAMPOL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/12/1992</t>
+          <t>26/03/2009</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>80074302</t>
+          <t>48214604</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAMARENA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BRIGIDA OLINDA</t>
+          <t>ADA VELINDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14/04/1977</t>
+          <t>18/12/1992</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41789336</t>
+          <t>80074302</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,20 +2895,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WALTER ROLANDO</t>
+          <t>BRIGIDA OLINDA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/05/1980</t>
+          <t>14/04/1977</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>73385444</t>
+          <t>41789336</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>URBANO PERCILES</t>
+          <t>WALTER ROLANDO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/05/1996</t>
+          <t>05/05/1980</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21/12/2011</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>60552816</t>
+          <t>73385444</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CAMARENA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MAYDA SAYURI</t>
+          <t>URBANO PERCILES</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>24/10/2007</t>
+          <t>10/05/1996</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>21/12/2011</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20118276</t>
+          <t>60552816</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELENA</t>
+          <t>MAYDA SAYURI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02/06/1978</t>
+          <t>24/10/2007</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06/12/2012</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,22 +3132,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>92123570</t>
+          <t>20118276</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>YOVITSA YANINA</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>07/08/2020</t>
+          <t>02/06/1978</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>06/12/2012</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,45 +3195,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20964970</t>
+          <t>92123570</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SEBASTIAN MAURO</t>
+          <t>YOVITSA YANINA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20/01/1962</t>
+          <t>07/08/2020</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>75847551</t>
+          <t>20964970</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FRAN SAUL</t>
+          <t>SEBASTIAN MAURO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/03/1999</t>
+          <t>20/01/1962</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>63421050</t>
+          <t>75847551</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GALAN</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JOSELO</t>
+          <t>FRAN SAUL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>06/01/2012</t>
+          <t>05/03/1999</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>09/05/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>92106434</t>
+          <t>63421050</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YOMPIRI</t>
+          <t>GALAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JAIRO</t>
+          <t>JOSELO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12/11/2020</t>
+          <t>06/01/2012</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>09/05/2013</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>40867686</t>
+          <t>92106434</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HUAMAN</t>
+          <t>YOMPIRI</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ROQUE JUVENAL</t>
+          <t>JAIRO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>03/05/1981</t>
+          <t>12/11/2020</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,22 +3510,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23682758</t>
+          <t>40867686</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ROQUE JUVENAL</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>27/03/1972</t>
+          <t>03/05/1981</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>92373689</t>
+          <t>23682758</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAMACIO</t>
+          <t>CLEMENTE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>YORAM HEYCOB</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24/05/2021</t>
+          <t>27/03/1972</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,40 +3636,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21006143</t>
+          <t>92373689</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>DAMACIO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE PARIONA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GREGORIA</t>
+          <t>YORAM HEYCOB</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>09/05/1955</t>
+          <t>24/05/2021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>76566154</t>
+          <t>21006143</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,30 +3709,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>DE PARIONA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>GREGORIA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15/01/1995</t>
+          <t>09/05/1955</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>26/10/2017</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>75875224</t>
+          <t>76566154</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BRANDO</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>26/11/2001</t>
+          <t>15/01/1995</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>26/10/2017</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>75875226</t>
+          <t>75875224</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>BRANDO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3849,11 +3849,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17/06/2004</t>
+          <t>26/11/2001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20416766</t>
+          <t>75875226</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CESARIO</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>01/11/1967</t>
+          <t>17/06/2004</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>75875221</t>
+          <t>20416766</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FILCLINTON BRAYAN</t>
+          <t>CESARIO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>14/11/1998</t>
+          <t>01/11/1967</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>63260158</t>
+          <t>75875221</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ROLANDO JHONY</t>
+          <t>FILCLINTON BRAYAN</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,11 +4038,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>15/04/2007</t>
+          <t>14/11/1998</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>49024751</t>
+          <t>63260158</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,35 +4087,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GEOVANA</t>
+          <t>ROLANDO JHONY</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15/02/1992</t>
+          <t>15/04/2007</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>09/09/2019</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,35 +4140,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>48975659</t>
+          <t>49024751</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>GEOVANA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>12/10/1982</t>
+          <t>15/02/1992</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>09/09/2019</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23685653</t>
+          <t>48975659</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4213,35 +4213,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DE CHAHUA</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11/02/1951</t>
+          <t>12/10/1982</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,45 +4266,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20993630</t>
+          <t>23685653</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GAGO</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>DE CHAHUA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>14/03/1970</t>
+          <t>11/02/1951</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,35 +4329,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21012969</t>
+          <t>20993630</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>GAGO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FLORA FELICITA</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>02/05/1977</t>
+          <t>14/03/1970</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,7 +4392,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>73715248</t>
+          <t>21012969</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4407,20 +4407,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ROY WILSON</t>
+          <t>FLORA FELICITA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>09/05/1995</t>
+          <t>02/05/1977</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>08/12/2011</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,45 +4455,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>61452157</t>
+          <t>73715248</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>HILARI MILEYDI</t>
+          <t>ROY WILSON</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>09/05/1995</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>08/12/2011</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>72579431</t>
+          <t>61452157</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4528,35 +4528,35 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ISAI ALEJANDRO</t>
+          <t>HILARI MILEYDI</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19/01/1996</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,22 +4581,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20988579</t>
+          <t>72579431</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GONZALO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>ISAI ALEJANDRO</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4605,16 +4605,16 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>26/05/1957</t>
+          <t>19/01/1996</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4644,45 +4644,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>74940517</t>
+          <t>20988579</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>GONZALO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>YOLINDA</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10/02/1997</t>
+          <t>26/05/1957</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,40 +4707,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>73446305</t>
+          <t>74940517</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HUARI</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BRANDUM MAIK</t>
+          <t>YOLINDA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01/09/1996</t>
+          <t>10/02/1997</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,45 +4770,45 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>93836589</t>
+          <t>73446305</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>HUARI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABEGAIL REYNA VALERIA</t>
+          <t>BRANDUM MAIK</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>07/03/2024</t>
+          <t>01/09/1996</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21002974</t>
+          <t>93836589</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>JULIA PRIMITIVA</t>
+          <t>ABEGAIL REYNA VALERIA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>16/09/1975</t>
+          <t>07/03/2024</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,22 +4896,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>75753510</t>
+          <t>21002974</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DIANA YULISA</t>
+          <t>JULIA PRIMITIVA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4920,21 +4920,21 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>28/12/1999</t>
+          <t>16/09/1975</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>47269907</t>
+          <t>75753510</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4969,30 +4969,30 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>EDINSON</t>
+          <t>DIANA YULISA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>09/09/1992</t>
+          <t>28/12/1999</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,45 +5022,45 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>92204627</t>
+          <t>47269907</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SARAI ABIGAIL</t>
+          <t>EDINSON</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>30/04/2020</t>
+          <t>09/09/1992</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5085,7 +5085,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20997750</t>
+          <t>92204627</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5095,35 +5095,35 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>SARAI ABIGAIL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>12/03/1970</t>
+          <t>30/04/2020</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,17 +5148,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>45474660</t>
+          <t>20997750</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5172,11 +5172,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>08/01/1986</t>
+          <t>12/03/1970</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>15/11/2012</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,22 +5211,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20991283</t>
+          <t>45474660</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JULCARIMA</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VICENTE HERMOGENES</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5235,11 +5235,11 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>19/04/1967</t>
+          <t>08/01/1986</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>15/11/2012</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,35 +5274,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>40153216</t>
+          <t>20991283</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>JULCARIMA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BARTOLO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>YOVANA DORINA</t>
+          <t>VICENTE HERMOGENES</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>12/04/1979</t>
+          <t>19/04/1967</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>73092414</t>
+          <t>40153216</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5347,30 +5347,30 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CERRON</t>
+          <t>BARTOLO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>YAYIR HUMBERTO</t>
+          <t>YOVANA DORINA</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>21/11/1999</t>
+          <t>12/04/1979</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>61618592</t>
+          <t>73092414</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CERRON</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LEONEL SMIT</t>
+          <t>YAYIR HUMBERTO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>12/12/1999</t>
+          <t>21/11/1999</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,22 +5463,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>21003014</t>
+          <t>61618592</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>LEONEL SMIT</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5487,21 +5487,21 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>13/11/1944</t>
+          <t>12/12/1999</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21003908</t>
+          <t>21003014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,11 +5550,11 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>28/11/1963</t>
+          <t>13/11/1944</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20411532</t>
+          <t>21003908</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DOMINGO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5613,11 +5613,11 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>15/06/1947</t>
+          <t>28/11/1963</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>48622054</t>
+          <t>20411532</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5662,30 +5662,30 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>DOMINGO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>19/01/1995</t>
+          <t>15/06/1947</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>08/06/2015</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>75875229</t>
+          <t>48622054</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5730,25 +5730,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CHARLYS ORLANDO</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>15/10/2001</t>
+          <t>19/01/1995</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>26/03/2018</t>
+          <t>08/06/2015</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>75875228</t>
+          <t>75875229</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>CHARLYS ORLANDO</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5802,11 +5802,11 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>14/10/2003</t>
+          <t>15/10/2001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5841,7 +5841,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>81417430</t>
+          <t>75875228</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5856,25 +5856,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SULLY JAZMIN</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>16/06/2014</t>
+          <t>14/10/2003</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>26/03/2018</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>44314926</t>
+          <t>81417430</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CELIA CARMEN</t>
+          <t>SULLY JAZMIN</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>03/06/1987</t>
+          <t>16/06/2014</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>47262412</t>
+          <t>44314926</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5977,25 +5977,25 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ABELANGE</t>
+          <t>CELIA CARMEN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>04/02/1992</t>
+          <t>03/06/1987</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,22 +6030,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21011849</t>
+          <t>47262412</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>GERONIMO EMILIANO</t>
+          <t>ABELANGE</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20/07/1958</t>
+          <t>04/02/1992</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,40 +6093,40 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>41755830</t>
+          <t>21011849</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>IRENE MARILU</t>
+          <t>GERONIMO EMILIANO</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>24/03/1983</t>
+          <t>20/07/1958</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">

--- a/exports/494_apalla-calabaza.xlsx
+++ b/exports/494_apalla-calabaza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2313,22 +2313,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>74276222</t>
+          <t>91305256</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AZAÑERO</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CORNEJO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SUMMER MANUEL</t>
+          <t>ISAAC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2337,16 +2337,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13/12/1998</t>
+          <t>27/04/2019</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2376,22 +2376,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>91305256</t>
+          <t>42007257</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>BORQUEZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORNEJO</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ISAAC</t>
+          <t>EVARISTO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27/04/2019</t>
+          <t>26/10/1981</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>42007257</t>
+          <t>45541017</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>TUPALAYA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EVARISTO</t>
+          <t>MARINA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>26/10/1981</t>
+          <t>16/07/1973</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2502,35 +2502,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>45541017</t>
+          <t>44308999</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BORQUEZ</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TUPALAYA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARINA</t>
+          <t>OLIVIO OSCAR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>16/07/1973</t>
+          <t>06/12/1986</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44308999</t>
+          <t>47537676</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>CAMARGO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OLIVIO OSCAR</t>
+          <t>JESUS DE NASARET</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2589,11 +2589,11 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/12/1986</t>
+          <t>28/05/1990</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2628,40 +2628,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>47537676</t>
+          <t>76940884</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>CAIRAMPOMA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAMARGO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JESUS DE NASARET</t>
+          <t>JANETH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28/05/1990</t>
+          <t>15/05/1999</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2691,45 +2691,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>76940884</t>
+          <t>60366731</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAIRAMPOMA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t>JHAMPOL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>15/05/1999</t>
+          <t>26/03/2009</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2754,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>60366731</t>
+          <t>48214604</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2764,35 +2764,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>JHAMPOL</t>
+          <t>ADA VELINDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>26/03/2009</t>
+          <t>18/12/1992</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,22 +2817,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>48214604</t>
+          <t>80074302</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAMARENA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ADA VELINDA</t>
+          <t>BRIGIDA OLINDA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18/12/1992</t>
+          <t>14/04/1977</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>80074302</t>
+          <t>41789336</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,20 +2895,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BRIGIDA OLINDA</t>
+          <t>WALTER ROLANDO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14/04/1977</t>
+          <t>05/05/1980</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>41789336</t>
+          <t>73385444</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WALTER ROLANDO</t>
+          <t>URBANO PERCILES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05/05/1980</t>
+          <t>10/05/1996</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>21/12/2011</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,45 +3006,45 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>73385444</t>
+          <t>60552816</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CAMARENA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>URBANO PERCILES</t>
+          <t>MAYDA SAYURI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10/05/1996</t>
+          <t>24/10/2007</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>21/12/2011</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,7 +3069,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>60552816</t>
+          <t>20118276</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MAYDA SAYURI</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>24/10/2007</t>
+          <t>02/06/1978</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>06/12/2012</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,22 +3132,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20118276</t>
+          <t>92123570</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ELENA</t>
+          <t>YOVITSA YANINA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3156,21 +3156,21 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02/06/1978</t>
+          <t>07/08/2020</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>06/12/2012</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,45 +3195,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>92123570</t>
+          <t>20964970</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>YOVITSA YANINA</t>
+          <t>SEBASTIAN MAURO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>07/08/2020</t>
+          <t>20/01/1962</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20964970</t>
+          <t>75847551</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SEBASTIAN MAURO</t>
+          <t>FRAN SAUL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,16 +3282,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20/01/1962</t>
+          <t>05/03/1999</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>75847551</t>
+          <t>63421050</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GALAN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FRAN SAUL</t>
+          <t>JOSELO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>05/03/1999</t>
+          <t>06/01/2012</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/05/2013</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>63421050</t>
+          <t>92106434</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GALAN</t>
+          <t>YOMPIRI</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JOSELO</t>
+          <t>JAIRO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>06/01/2012</t>
+          <t>12/11/2020</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>09/05/2013</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>92106434</t>
+          <t>40867686</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YOMPIRI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JAIRO</t>
+          <t>ROQUE JUVENAL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12/11/2020</t>
+          <t>03/05/1981</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,22 +3510,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>40867686</t>
+          <t>23682758</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>CLEMENTE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>CASTRO</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HUAMAN</t>
-        </is>
-      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ROQUE JUVENAL</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,11 +3534,11 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>03/05/1981</t>
+          <t>27/03/1972</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,7 +3573,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23682758</t>
+          <t>72288532</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ABEL CRISTIAN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>27/03/1972</t>
+          <t>28/10/2005</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -6156,40 +6156,40 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>61965017</t>
+          <t>41755830</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>JOSEPH BRYAN</t>
+          <t>IRENE MARILU</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>18/08/2009</t>
+          <t>24/03/1983</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,7 +6219,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>80597078</t>
+          <t>61965017</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6229,35 +6229,35 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CHIPANA</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DIANA NANCY</t>
+          <t>JOSEPH BRYAN</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>10/12/1972</t>
+          <t>18/08/2009</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>17/12/2020</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,35 +6282,35 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>43515291</t>
+          <t>80597078</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>CHIPANA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BRAMBLI</t>
+          <t>DIANA NANCY</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>24/12/1985</t>
+          <t>10/12/1972</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>17/12/2020</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,45 +6345,45 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>20411989</t>
+          <t>94535457</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MORALEZ</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CEFERINA</t>
+          <t>BRAYDEN DARIEL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>06/11/1957</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,22 +6408,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>46139062</t>
+          <t>43515291</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NAIVARES</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>BRAMBLI</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6432,11 +6432,11 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14/10/1989</t>
+          <t>24/12/1985</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,22 +6471,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>94677493</t>
+          <t>20411989</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>MORALEZ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CERRON</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CATALINA ORIANA BELEN</t>
+          <t>CEFERINA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6495,21 +6495,21 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>06/11/1957</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>91259214</t>
+          <t>46139062</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>NAIVARES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BARTOLO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>JHOSMEL AXEL</t>
+          <t>MARCOS</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>14/10/1989</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,45 +6597,45 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>75843632</t>
+          <t>94677493</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>CERRON</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>FRANK ELISEO</t>
+          <t>CATALINA ORIANA BELEN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>15/12/2006</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>25/06/2013</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,22 +6660,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>21003053</t>
+          <t>91259214</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>BARTOLO</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ELOY MIGUEL</t>
+          <t>JHOSMEL AXEL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6684,16 +6684,16 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>29/12/1972</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,22 +6723,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20996640</t>
+          <t>75843632</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t>FRANK ELISEO</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6747,21 +6747,21 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>06/09/1969</t>
+          <t>15/12/2006</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>25/06/2013</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,40 +6786,40 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20985500</t>
+          <t>21003053</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t>ELOY MIGUEL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>07/06/1963</t>
+          <t>29/12/1972</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,35 +6849,35 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>47769339</t>
+          <t>20996640</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>02/08/1971</t>
+          <t>06/09/1969</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,22 +6912,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>74281901</t>
+          <t>20985500</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CANCHUMONIA</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LUZ MARIA</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6936,21 +6936,21 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>23/08/1999</t>
+          <t>07/06/1963</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,35 +6975,35 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>80039881</t>
+          <t>47769339</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>FELIPE</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>15/01/1968</t>
+          <t>02/08/1971</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7038,22 +7038,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>60202528</t>
+          <t>74281901</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PAYTAMPOMA</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VELIS</t>
+          <t>CANCHUMONIA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MERLIN SARITA</t>
+          <t>LUZ MARIA</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7062,11 +7062,11 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>01/10/2006</t>
+          <t>23/08/1999</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20012234</t>
+          <t>80039881</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>FELIPE</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,16 +7125,16 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>27/03/1961</t>
+          <t>15/01/1968</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,45 +7164,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>43004393</t>
+          <t>60202528</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PAYTAMPOMA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELIS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ALBINO</t>
+          <t>MERLIN SARITA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>05/05/1985</t>
+          <t>01/10/2006</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>44163338</t>
+          <t>20012234</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PIRCA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MAEL ALIN</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,21 +7251,21 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>06/02/1987</t>
+          <t>27/03/1961</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>17/10/2018</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>43625177</t>
+          <t>43004393</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ROBER ROSENDO</t>
+          <t>ALBINO</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>28/01/1982</t>
+          <t>05/05/1985</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7353,22 +7353,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>47799382</t>
+          <t>44163338</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PIRCA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BORQUIS</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CAYO EDSON</t>
+          <t>MAEL ALIN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7377,11 +7377,11 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>27/11/1989</t>
+          <t>06/02/1987</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/10/2018</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>41918492</t>
+          <t>43625177</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ERNAN</t>
+          <t>ROBER ROSENDO</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10/02/1982</t>
+          <t>28/01/1982</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>40303621</t>
+          <t>47799382</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>BORQUIS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ALBERT</t>
+          <t>CAYO EDSON</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,11 +7503,11 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>18/12/1978</t>
+          <t>27/11/1989</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,35 +7542,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>77213217</t>
+          <t>41918492</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>OLIVIA</t>
+          <t>ERNAN</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10/08/1995</t>
+          <t>10/02/1982</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>20973300</t>
+          <t>40303621</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>AMADEO AGAPITO</t>
+          <t>ALBERT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>24/03/1945</t>
+          <t>18/12/1978</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>16/12/2020</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>72455623</t>
+          <t>77213217</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>GUADALUPE YESENIA</t>
+          <t>OLIVIA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,11 +7692,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>26/05/1996</t>
+          <t>10/08/1995</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20412069</t>
+          <t>20973300</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LANDEON</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>MAXIMO PABLO</t>
+          <t>AMADEO AGAPITO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20/07/1967</t>
+          <t>24/03/1945</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>16/12/2020</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>20417099</t>
+          <t>72455623</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>MARCELINA</t>
+          <t>GUADALUPE YESENIA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7818,11 +7818,11 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>16/01/1971</t>
+          <t>26/05/1996</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,35 +7857,35 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>40017830</t>
+          <t>20412069</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ROQUE</t>
+          <t>LANDEON</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>JULIA MARTHA</t>
+          <t>MAXIMO PABLO</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>12/07/1978</t>
+          <t>20/07/1967</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,40 +7920,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>22989030</t>
+          <t>20417099</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>MARCELINA</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>05/10/1963</t>
+          <t>16/01/1971</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,22 +7983,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>45953849</t>
+          <t>40017830</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ROQUE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SABINA DONATA</t>
+          <t>JULIA MARTHA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>30/12/1980</t>
+          <t>12/07/1978</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>09/10/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>23560662</t>
+          <t>22989030</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>31/08/1973</t>
+          <t>05/10/1963</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,40 +8109,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>23369270</t>
+          <t>45953849</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HUAYNACCERO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>SABINA DONATA</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>10/11/1959</t>
+          <t>30/12/1980</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/10/2012</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,35 +8172,35 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>44464638</t>
+          <t>23560662</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EVA YUNILDA</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>11/03/1986</t>
+          <t>31/08/1973</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>75997417</t>
+          <t>23369270</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>HUAYNACCERO</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>KENYI</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>01/11/1999</t>
+          <t>10/11/1959</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>92432475</t>
+          <t>44464638</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GAELA CAYETANA</t>
+          <t>EVA YUNILDA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>04/07/2021</t>
+          <t>11/03/1986</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>92370866</t>
+          <t>75997417</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VILLAR</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>JEYCO WILMER</t>
+          <t>KENYI</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>22/05/2021</t>
+          <t>01/11/1999</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,40 +8424,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>60501472</t>
+          <t>92432475</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>IDOLIO IVAN</t>
+          <t>GAELA CAYETANA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>07/06/2007</t>
+          <t>04/07/2021</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>30/05/2018</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,40 +8487,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>28242836</t>
+          <t>92370866</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VILCAMICHE</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PINCO</t>
+          <t>VILLAR</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ESTEFA</t>
+          <t>JEYCO WILMER</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>01/04/1961</t>
+          <t>22/05/2021</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>41934706</t>
+          <t>60501472</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>HELVER ALIANDRO</t>
+          <t>IDOLIO IVAN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,21 +8574,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20/12/1978</t>
+          <t>07/06/2007</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>30/05/2018</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,45 +8613,45 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>76040982</t>
+          <t>28242836</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>YAÑAC</t>
+          <t>VILCAMICHE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PINCO</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>JHORHG GHENSBEL</t>
+          <t>ESTEFA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>09/03/2004</t>
+          <t>01/04/1961</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,35 +8676,35 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>21011829</t>
+          <t>41934706</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DE HUAYCAÑE</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HERLINDA AURELIA</t>
+          <t>HELVER ALIANDRO</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>25/01/1967</t>
+          <t>20/12/1978</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>20412006</t>
+          <t>76040982</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>YAÑAC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DE ORELLANA</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>FORTUNATA</t>
+          <t>JHORHG GHENSBEL</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>07/06/1959</t>
+          <t>09/03/2004</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>76683959</t>
+          <t>21011829</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,25 +8812,25 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>DE HUAYCAÑE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>SATURNINO HENRY</t>
+          <t>HERLINDA AURELIA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>13/09/1994</t>
+          <t>25/01/1967</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8865,63 +8865,189 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>20412006</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DE ORELLANA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>FORTUNATA</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>67</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>07/06/1959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>5.ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>11/02/2013</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>76683959</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>YUPANQUI</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>VILLANUEVA</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SATURNINO HENRY</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>32</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>13/09/1994</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>4.ADULTO</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>AFILIACION PPDD</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>30/09/2014</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M136" t="n">
+        <v>120605</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>76648032</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>ZARZOSA</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>CHAMORRO</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>JAVIER ALEX</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>Masculino</t>
         </is>
       </c>
-      <c r="F135" t="n">
+      <c r="F137" t="n">
         <v>32</v>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>24/06/1994</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>4.ADULTO</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>AFILIACION PPDD</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>30/09/2014</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M135" t="n">
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>PAMPA HERMOSA</t>
+        </is>
+      </c>
+      <c r="M137" t="n">
         <v>120605</v>
       </c>
     </row>

--- a/exports/494_apalla-calabaza.xlsx
+++ b/exports/494_apalla-calabaza.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2628,45 +2628,45 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>76940884</t>
+          <t>60366731</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CAIRAMPOMA</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SANTOS</t>
+          <t>CALDERON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JANETH</t>
+          <t>JHAMPOL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>15/05/1999</t>
+          <t>26/03/2009</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>60366731</t>
+          <t>48214604</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2701,35 +2701,35 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALDERON</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JHAMPOL</t>
+          <t>ADA VELINDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>26/03/2009</t>
+          <t>18/12/1992</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>05/04/2025</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2754,22 +2754,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>48214604</t>
+          <t>80074302</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>CAMARENA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>PORTILLO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ADA VELINDA</t>
+          <t>BRIGIDA OLINDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2778,11 +2778,11 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18/12/1992</t>
+          <t>14/04/1977</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>05/04/2025</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2817,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>80074302</t>
+          <t>41789336</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2832,20 +2832,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BRIGIDA OLINDA</t>
+          <t>WALTER ROLANDO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>14/04/1977</t>
+          <t>05/05/1980</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>15/05/2018</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41789336</t>
+          <t>73385444</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WALTER ROLANDO</t>
+          <t>URBANO PERCILES</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2904,11 +2904,11 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/05/1980</t>
+          <t>10/05/1996</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>15/05/2018</t>
+          <t>21/12/2011</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2943,45 +2943,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>73385444</t>
+          <t>60552816</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAMARENA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PORTILLO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>URBANO PERCILES</t>
+          <t>MAYDA SAYURI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10/05/1996</t>
+          <t>24/10/2007</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>21/12/2011</t>
+          <t>28/03/2013</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3006,7 +3006,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>60552816</t>
+          <t>20118276</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MAYDA SAYURI</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3030,21 +3030,21 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>24/10/2007</t>
+          <t>02/06/1978</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>28/03/2013</t>
+          <t>06/12/2012</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3069,22 +3069,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20118276</t>
+          <t>92123570</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ELENA</t>
+          <t>YOVITSA YANINA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3093,21 +3093,21 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02/06/1978</t>
+          <t>07/08/2020</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>06/12/2012</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3132,45 +3132,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>92123570</t>
+          <t>20964970</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>YOVITSA YANINA</t>
+          <t>SEBASTIAN MAURO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>07/08/2020</t>
+          <t>20/01/1962</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3195,22 +3195,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20964970</t>
+          <t>75847551</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SEBASTIAN MAURO</t>
+          <t>FRAN SAUL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20/01/1962</t>
+          <t>05/03/1999</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>75847551</t>
+          <t>63421050</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>CASO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>GALAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FRAN SAUL</t>
+          <t>JOSELO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3282,21 +3282,21 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05/03/1999</t>
+          <t>06/01/2012</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/05/2013</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3321,22 +3321,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>63421050</t>
+          <t>92106434</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASO</t>
+          <t>CASTAÑEDA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GALAN</t>
+          <t>YOMPIRI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>JOSELO</t>
+          <t>JAIRO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>06/01/2012</t>
+          <t>12/11/2020</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>09/05/2013</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3384,22 +3384,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>92106434</t>
+          <t>40867686</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASTAÑEDA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YOMPIRI</t>
+          <t>HUAMAN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>JAIRO</t>
+          <t>ROQUE JUVENAL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>12/11/2020</t>
+          <t>03/05/1981</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3447,22 +3447,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>40867686</t>
+          <t>23682758</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>CLEMENTE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>CASTRO</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>HUAMAN</t>
-        </is>
-      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ROQUE JUVENAL</t>
+          <t>JUAN</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3471,11 +3471,11 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>03/05/1981</t>
+          <t>27/03/1972</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/09/2024</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3510,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23682758</t>
+          <t>72288532</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>ABEL CRISTIAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3534,16 +3534,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>27/03/1972</t>
+          <t>28/10/2005</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>24/09/2024</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3573,22 +3573,22 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>72288532</t>
+          <t>92373689</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CLEMENTE</t>
+          <t>DAMACIO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ABEL CRISTIAN</t>
+          <t>YORAM HEYCOB</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3597,21 +3597,21 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>28/10/2005</t>
+          <t>24/05/2021</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3636,40 +3636,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>92373689</t>
+          <t>21006143</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DAMACIO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>DE PARIONA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>YORAM HEYCOB</t>
+          <t>GREGORIA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>24/05/2021</t>
+          <t>09/05/1955</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3699,7 +3699,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21006143</t>
+          <t>76566154</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3709,30 +3709,30 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DE PARIONA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GREGORIA</t>
+          <t>CARLOS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>09/05/1955</t>
+          <t>15/01/1995</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>26/10/2017</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>76566154</t>
+          <t>75875224</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>BRANDO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3786,16 +3786,16 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>15/01/1995</t>
+          <t>26/11/2001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>26/10/2017</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3825,7 +3825,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>75875224</t>
+          <t>75875226</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BRANDO</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3849,11 +3849,11 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>26/11/2001</t>
+          <t>17/06/2004</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3888,7 +3888,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>75875226</t>
+          <t>20416766</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>CESARIO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3912,21 +3912,21 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17/06/2004</t>
+          <t>01/11/1967</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>23/10/2013</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3951,22 +3951,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20416766</t>
+          <t>75875221</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CESARIO</t>
+          <t>FILCLINTON BRAYAN</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3975,21 +3975,21 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>01/11/1967</t>
+          <t>14/11/1998</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BENEFICIARIOS DE REPARACIONES EN SALUD</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>23/10/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4014,22 +4014,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>75875221</t>
+          <t>63260158</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FILCLINTON BRAYAN</t>
+          <t>ROLANDO JHONY</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4038,11 +4038,11 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>14/11/1998</t>
+          <t>15/04/2007</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>14/11/2013</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>63260158</t>
+          <t>49024751</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4087,35 +4087,35 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>ENRIQUE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ROLANDO JHONY</t>
+          <t>GEOVANA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15/04/2007</t>
+          <t>15/02/1992</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>14/11/2013</t>
+          <t>09/09/2019</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4140,35 +4140,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>49024751</t>
+          <t>48975659</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>CAPCHA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>GEOVANA</t>
+          <t>RAUL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15/02/1992</t>
+          <t>12/10/1982</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>VULNERABILIDAD SANITARIA - DISCAPACIDAD SEVERA (DS Nº 002-2020-SA)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>09/09/2019</t>
+          <t>17/04/2024</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>48975659</t>
+          <t>23685653</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4213,35 +4213,35 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CAPCHA</t>
+          <t>DE CHAHUA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>RAUL</t>
+          <t>LOURDES</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>12/10/1982</t>
+          <t>11/02/1951</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>17/04/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4266,45 +4266,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>23685653</t>
+          <t>20993630</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>GAGO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE CHAHUA</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LOURDES</t>
+          <t>PEDRO PABLO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11/02/1951</t>
+          <t>14/03/1970</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/04/2024</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4329,35 +4329,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20993630</t>
+          <t>21012969</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GAGO</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>PAUCAR</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PEDRO PABLO</t>
+          <t>FLORA FELICITA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>14/03/1970</t>
+          <t>02/05/1977</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>18/04/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4392,22 +4392,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21012969</t>
+          <t>61452157</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FLORA FELICITA</t>
+          <t>HILARI MILEYDI</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4416,21 +4416,21 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>02/05/1977</t>
+          <t>09/08/2008</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4455,22 +4455,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>73715248</t>
+          <t>72579431</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PAUCAR</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ROY WILSON</t>
+          <t>ISAI ALEJANDRO</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4479,11 +4479,11 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09/05/1995</t>
+          <t>19/01/1996</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>08/12/2011</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4518,45 +4518,45 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>61452157</t>
+          <t>20988579</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>SOLANO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>HILARI MILEYDI</t>
+          <t>GERMAN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09/08/2008</t>
+          <t>26/05/1957</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4581,45 +4581,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>72579431</t>
+          <t>74940517</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>HINOJOSA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ISAI ALEJANDRO</t>
+          <t>YOLINDA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>19/01/1996</t>
+          <t>10/02/1997</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>30/07/2025</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4644,22 +4644,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20988579</t>
+          <t>73446305</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GONZALO</t>
+          <t>HUARI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOLANO</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GERMAN</t>
+          <t>BRANDUM MAIK</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4668,21 +4668,21 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>26/05/1957</t>
+          <t>01/09/1996</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>06/02/2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4707,22 +4707,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>74940517</t>
+          <t>93836589</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HINOJOSA</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>YOLINDA</t>
+          <t>ABEGAIL REYNA VALERIA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4731,21 +4731,21 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10/02/1997</t>
+          <t>07/03/2024</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>30/07/2025</t>
+          <t>20/07/2024</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4770,35 +4770,35 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>73446305</t>
+          <t>21002974</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUARI</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QUISPE</t>
+          <t>HINOSTROZA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BRANDUM MAIK</t>
+          <t>JULIA PRIMITIVA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01/09/1996</t>
+          <t>16/09/1975</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>06/02/2026</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4833,22 +4833,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>93836589</t>
+          <t>75753510</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ABEGAIL REYNA VALERIA</t>
+          <t>DIANA YULISA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4857,21 +4857,21 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>07/03/2024</t>
+          <t>28/12/1999</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>20/07/2024</t>
+          <t>18/09/2011</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4896,35 +4896,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>21002974</t>
+          <t>47269907</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HINOSTROZA</t>
+          <t>MERCADO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>JULIA PRIMITIVA</t>
+          <t>EDINSON</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>16/09/1975</t>
+          <t>09/09/1992</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>23/09/2013</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4959,22 +4959,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>75753510</t>
+          <t>92204627</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DIANA YULISA</t>
+          <t>SARAI ABIGAIL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4983,21 +4983,21 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>28/12/1999</t>
+          <t>30/04/2020</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>18/09/2011</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5022,22 +5022,22 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>47269907</t>
+          <t>20997750</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>HUAYCAÑI</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MERCADO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EDINSON</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5046,11 +5046,11 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>09/09/1992</t>
+          <t>12/03/1970</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5085,45 +5085,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>92204627</t>
+          <t>45474660</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>VILLEGAS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SARAI ABIGAIL</t>
+          <t>VICTOR</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>30/04/2020</t>
+          <t>08/01/1986</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>15/11/2012</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5148,22 +5148,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20997750</t>
+          <t>20991283</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HUAYCAÑI</t>
+          <t>JULCARIMA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>VICENTE HERMOGENES</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5172,11 +5172,11 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>12/03/1970</t>
+          <t>19/04/1967</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>23/09/2013</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5211,35 +5211,35 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>45474660</t>
+          <t>40153216</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VILLEGAS</t>
+          <t>BARTOLO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VICTOR</t>
+          <t>YOVANA DORINA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>08/01/1986</t>
+          <t>12/04/1979</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>15/11/2012</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5274,22 +5274,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20991283</t>
+          <t>73092414</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JULCARIMA</t>
+          <t>LIZARRAGA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>CERRON</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VICENTE HERMOGENES</t>
+          <t>YAYIR HUMBERTO</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5298,16 +5298,16 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19/04/1967</t>
+          <t>21/11/1999</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>24/09/2025</t>
+          <t>04/04/2025</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5337,7 +5337,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>40153216</t>
+          <t>61618592</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5347,30 +5347,30 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BARTOLO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>YOVANA DORINA</t>
+          <t>LEONEL SMIT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12/04/1979</t>
+          <t>12/12/1999</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5400,22 +5400,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>73092414</t>
+          <t>21003014</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CERRON</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>YAYIR HUMBERTO</t>
+          <t>DIEGO</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5424,21 +5424,21 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>21/11/1999</t>
+          <t>13/11/1944</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>04/04/2025</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5463,22 +5463,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>61618592</t>
+          <t>21003908</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LIZARRAGA</t>
+          <t>MACHUCA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>TAIPE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LEONEL SMIT</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5487,21 +5487,21 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12/12/1999</t>
+          <t>28/11/1963</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5526,22 +5526,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>21003014</t>
+          <t>20411532</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DIEGO</t>
+          <t>DOMINGO</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5550,11 +5550,11 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13/11/1944</t>
+          <t>15/06/1947</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>08/07/2013</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5589,40 +5589,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>21003908</t>
+          <t>48622054</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MACHUCA</t>
+          <t>MALDONADO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TAIPE</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>ESPERANZA</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>28/11/1963</t>
+          <t>19/01/1995</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>08/06/2015</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20411532</t>
+          <t>75875229</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BRAVO</t>
+          <t>HUARINGA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>DOMINGO</t>
+          <t>CHARLYS ORLANDO</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>15/06/1947</t>
+          <t>15/10/2001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>08/07/2013</t>
+          <t>26/03/2018</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>48622054</t>
+          <t>75875228</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5730,25 +5730,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ESPERANZA</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>19/01/1995</t>
+          <t>14/10/2003</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>08/06/2015</t>
+          <t>26/03/2018</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>75875229</t>
+          <t>81417430</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5793,25 +5793,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CHARLYS ORLANDO</t>
+          <t>SULLY JAZMIN</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>15/10/2001</t>
+          <t>16/06/2014</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>26/03/2018</t>
+          <t>19/10/2016</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5841,7 +5841,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>75875228</t>
+          <t>44314926</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>LLANCO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>CELIA CARMEN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>14/10/2003</t>
+          <t>03/06/1987</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>26/03/2018</t>
+          <t>09/05/2022</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5904,7 +5904,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>81417430</t>
+          <t>47262412</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5914,30 +5914,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HUARINGA</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SULLY JAZMIN</t>
+          <t>ABELANGE</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>16/06/2014</t>
+          <t>04/02/1992</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>19/10/2016</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5967,40 +5967,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>44314926</t>
+          <t>21011849</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LLANCO</t>
+          <t>ESPINOZA</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CELIA CARMEN</t>
+          <t>GERONIMO EMILIANO</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>03/06/1987</t>
+          <t>20/07/1958</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>03/10/2022</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6030,35 +6030,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>47262412</t>
+          <t>41755830</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MALDONADO</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>CARBAJAL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ABELANGE</t>
+          <t>IRENE MARILU</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>04/02/1992</t>
+          <t>24/03/1983</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6093,22 +6093,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>21011849</t>
+          <t>61965017</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ESPINOZA</t>
+          <t>CANCHUMUNIA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>GERONIMO EMILIANO</t>
+          <t>JOSEPH BRYAN</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20/07/1958</t>
+          <t>18/08/2009</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>2.ADOLESCENTE</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>03/10/2022</t>
+          <t>10/02/2025</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>41755830</t>
+          <t>80597078</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CARBAJAL</t>
+          <t>CHIPANA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>IRENE MARILU</t>
+          <t>DIANA NANCY</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6180,11 +6180,11 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>24/03/1983</t>
+          <t>10/12/1972</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>17/12/2020</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6219,22 +6219,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>61965017</t>
+          <t>94535457</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CANCHUMUNIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>JOSEPH BRYAN</t>
+          <t>BRAYDEN DARIEL</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6243,21 +6243,21 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18/08/2009</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2.ADOLESCENTE</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>10/02/2025</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6282,35 +6282,35 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>80597078</t>
+          <t>43515291</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MONTALVO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CHIPANA</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DIANA NANCY</t>
+          <t>BRAMBLI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>10/12/1972</t>
+          <t>24/12/1985</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>17/12/2020</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6345,45 +6345,45 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>94535457</t>
+          <t>20411989</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>MORALEZ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BRAYDEN DARIEL</t>
+          <t>CEFERINA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>06/11/1957</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6408,45 +6408,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>43515291</t>
+          <t>94677493</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MONTALVO</t>
+          <t>ORELLANA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ZARATE</t>
+          <t>CERRON</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BRAMBLI</t>
+          <t>CATALINA ORIANA BELEN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>24/12/1985</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6471,45 +6471,45 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>20411989</t>
+          <t>91259214</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MORALEZ</t>
+          <t>PACHECO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>BARTOLO</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CEFERINA</t>
+          <t>JHOSMEL AXEL</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>06/11/1957</t>
+          <t>01/04/2019</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6534,22 +6534,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>46139062</t>
+          <t>75843632</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NAIVARES</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>AMES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>MARCOS</t>
+          <t>FRANK ELISEO</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6558,21 +6558,21 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>14/10/1989</t>
+          <t>15/12/2006</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>25/06/2013</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6597,45 +6597,45 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>94677493</t>
+          <t>21003053</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ORELLANA</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CERRON</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CATALINA ORIANA BELEN</t>
+          <t>ELOY MIGUEL</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>29/12/1972</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NIÑOS ENTRE 0 A 5 AÑOS (DS Nº 305-2014-EF)</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6660,22 +6660,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>91259214</t>
+          <t>20996640</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PACHECO</t>
+          <t>PALOMINO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BARTOLO</t>
+          <t>DE LA CRUZ</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>JHOSMEL AXEL</t>
+          <t>RUBEN</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6684,21 +6684,21 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>01/04/2019</t>
+          <t>06/09/1969</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,45 +6723,45 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>75843632</t>
+          <t>20985500</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AMES</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>FRANK ELISEO</t>
+          <t>LUCIA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>15/12/2006</t>
+          <t>07/06/1963</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ESCOLARES QALI WARMA (LEY Nº 30061)</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>25/06/2013</t>
+          <t>18/10/2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6786,35 +6786,35 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>21003053</t>
+          <t>47769339</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>PARADO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>QUIÑONEZ</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ELOY MIGUEL</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>29/12/1972</t>
+          <t>02/08/1971</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6849,40 +6849,40 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20996640</t>
+          <t>74281901</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PALOMINO</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DE LA CRUZ</t>
+          <t>CANCHUMONIA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>RUBEN</t>
+          <t>LUZ MARIA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>06/09/1969</t>
+          <t>23/08/1999</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6912,45 +6912,45 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20985500</t>
+          <t>80039881</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>PARIONA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>HUAYCAÑE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LUCIA</t>
+          <t>FELIPE</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>07/06/1963</t>
+          <t>15/01/1968</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>09/05/2022</t>
+          <t>05/12/2012</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6975,22 +6975,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>47769339</t>
+          <t>60202528</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PARADO</t>
+          <t>PAYTAMPOMA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>QUIÑONEZ</t>
+          <t>VELIS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>MERLIN SARITA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>02/08/1971</t>
+          <t>01/10/2006</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7038,40 +7038,40 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>74281901</t>
+          <t>20012234</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CANCHUMONIA</t>
+          <t>MAYTA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LUZ MARIA</t>
+          <t>FRANCISCO</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23/08/1999</t>
+          <t>27/03/1961</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7101,22 +7101,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>80039881</t>
+          <t>43004393</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PARIONA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HUAYCAÑE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FELIPE</t>
+          <t>ALBINO</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7125,11 +7125,11 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>15/01/1968</t>
+          <t>05/05/1985</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>05/12/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7164,40 +7164,40 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>60202528</t>
+          <t>44163338</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PAYTAMPOMA</t>
+          <t>PIRCA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VELIS</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>MERLIN SARITA</t>
+          <t>MAEL ALIN</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>01/10/2006</t>
+          <t>06/02/1987</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>17/10/2018</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7227,22 +7227,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20012234</t>
+          <t>43625177</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MAYTA</t>
+          <t>CERVANTES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FRANCISCO</t>
+          <t>ROBER ROSENDO</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7251,16 +7251,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>27/03/1961</t>
+          <t>28/01/1982</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7290,22 +7290,22 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>43004393</t>
+          <t>47799382</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BORQUIS</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ALBINO</t>
+          <t>CAYO EDSON</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>05/05/1985</t>
+          <t>27/11/1989</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7353,22 +7353,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>44163338</t>
+          <t>41918492</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PIRCA</t>
+          <t>PORRAS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>PAITAMPOMA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MAEL ALIN</t>
+          <t>ERNAN</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7377,11 +7377,11 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>06/02/1987</t>
+          <t>10/02/1982</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>17/10/2018</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7416,22 +7416,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>43625177</t>
+          <t>90114796</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>QUISPE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CERVANTES</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ROBER ROSENDO</t>
+          <t>JAIRO SMITH</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7440,16 +7440,16 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>28/01/1982</t>
+          <t>09/03/2017</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7479,22 +7479,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>47799382</t>
+          <t>40303621</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BORQUIS</t>
+          <t>RAYMUNDO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CAYO EDSON</t>
+          <t>ALBERT</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7503,11 +7503,11 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>27/11/1989</t>
+          <t>18/12/1978</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7542,35 +7542,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>41918492</t>
+          <t>77213217</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PORRAS</t>
+          <t>RICRA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PAITAMPOMA</t>
+          <t>EGOAVIL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ERNAN</t>
+          <t>OLIVIA</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>10/02/1982</t>
+          <t>10/08/1995</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7605,22 +7605,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>40303621</t>
+          <t>20973300</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>ROBLES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>RAYMUNDO</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ALBERT</t>
+          <t>AMADEO AGAPITO</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7629,16 +7629,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>18/12/1978</t>
+          <t>24/03/1945</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>16/12/2020</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7668,22 +7668,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>77213217</t>
+          <t>72455623</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>RICRA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EGOAVIL</t>
+          <t>LOPE</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>OLIVIA</t>
+          <t>GUADALUPE YESENIA</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7692,11 +7692,11 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>10/08/1995</t>
+          <t>26/05/1996</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>24/01/2020</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7731,22 +7731,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>20973300</t>
+          <t>20412069</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ROBLES</t>
+          <t>ROSALES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>LANDEON</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AMADEO AGAPITO</t>
+          <t>MAXIMO PABLO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7755,16 +7755,16 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>24/03/1945</t>
+          <t>20/07/1967</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>16/12/2020</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7794,22 +7794,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>72455623</t>
+          <t>20417099</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>SALAZAR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LOPE</t>
+          <t>CAJA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GUADALUPE YESENIA</t>
+          <t>MARCELINA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7818,11 +7818,11 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>26/05/1996</t>
+          <t>16/01/1971</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>24/01/2020</t>
+          <t>21/03/2024</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7857,35 +7857,35 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20412069</t>
+          <t>40017830</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ROSALES</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LANDEON</t>
+          <t>ROQUE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MAXIMO PABLO</t>
+          <t>JULIA MARTHA</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20/07/1967</t>
+          <t>12/07/1978</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7920,40 +7920,40 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>20417099</t>
+          <t>22989030</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SALAZAR</t>
+          <t>SARMIENTO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CAJA</t>
+          <t>PRIMO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MARCELINA</t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>16/01/1971</t>
+          <t>05/10/1963</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>21/03/2024</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7983,22 +7983,22 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>40017830</t>
+          <t>45953849</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>SOSA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ROQUE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>JULIA MARTHA</t>
+          <t>SABINA DONATA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8007,11 +8007,11 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>12/07/1978</t>
+          <t>30/12/1980</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>09/10/2012</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8046,22 +8046,22 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>22989030</t>
+          <t>23560662</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SARMIENTO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PRIMO</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>RAMON</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8070,21 +8070,21 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>05/10/1963</t>
+          <t>31/08/1973</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>27/11/2025</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8109,40 +8109,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>45953849</t>
+          <t>23369270</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SOSA</t>
+          <t>TORRE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>HUAYNACCERO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SABINA DONATA</t>
+          <t>ANDRES</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>30/12/1980</t>
+          <t>10/11/1959</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>09/10/2012</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8172,35 +8172,35 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>23560662</t>
+          <t>44464638</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>RAMON</t>
+          <t>EVA YUNILDA</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>31/08/1973</t>
+          <t>11/03/1986</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>27/11/2025</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8235,22 +8235,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>23369270</t>
+          <t>75997417</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TORRE</t>
+          <t>VALERO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HUAYNACCERO</t>
+          <t>ROJAS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ANDRES</t>
+          <t>KENYI</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>10/11/1959</t>
+          <t>01/11/1999</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8298,22 +8298,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>44464638</t>
+          <t>92432475</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>INGA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EVA YUNILDA</t>
+          <t>GAELA CAYETANA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8322,16 +8322,16 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>11/03/1986</t>
+          <t>04/07/2021</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8361,22 +8361,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>75997417</t>
+          <t>92370866</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VALERO</t>
+          <t>VELASQUEZ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ROJAS</t>
+          <t>VILLAR</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>KENYI</t>
+          <t>JEYCO WILMER</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8385,21 +8385,21 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>01/11/1999</t>
+          <t>22/05/2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>1.NIÑO</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8424,40 +8424,40 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>92432475</t>
+          <t>60501472</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VELIZ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>INGA</t>
+          <t>APOLINARIO</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GAELA CAYETANA</t>
+          <t>IDOLIO IVAN</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>04/07/2021</t>
+          <t>07/06/2007</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/05/2018</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8487,40 +8487,40 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>92370866</t>
+          <t>28242836</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VELASQUEZ</t>
+          <t>VILCAMICHE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VILLAR</t>
+          <t>PINCO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>JEYCO WILMER</t>
+          <t>ESTEFA</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>22/05/2021</t>
+          <t>01/04/1961</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>1.NIÑO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8550,22 +8550,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>60501472</t>
+          <t>41934706</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VELIZ</t>
+          <t>VILLALOBOS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>APOLINARIO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>IDOLIO IVAN</t>
+          <t>HELVER ALIANDRO</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8574,21 +8574,21 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>07/06/2007</t>
+          <t>20/12/1978</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>30/05/2018</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8613,22 +8613,22 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>28242836</t>
+          <t>71862214</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VILCAMICHE</t>
+          <t>YAURI</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PINCO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ESTEFA</t>
+          <t>DINA KELY</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8637,16 +8637,16 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>01/04/1961</t>
+          <t>08/09/1997</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8676,22 +8676,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>41934706</t>
+          <t>76040982</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VILLALOBOS</t>
+          <t>YAÑAC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>HELVER ALIANDRO</t>
+          <t>JHORHG GHENSBEL</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8700,21 +8700,21 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20/12/1978</t>
+          <t>09/03/2004</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>3.JOVEN</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>AFILIACION PPDD</t>
+          <t>AFILIACION MASIVA DE OFICIO</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8739,45 +8739,45 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>76040982</t>
+          <t>21011829</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>YAÑAC</t>
+          <t>YUPANQUI</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>DE HUAYCAÑE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>JHORHG GHENSBEL</t>
+          <t>HERLINDA AURELIA</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>09/03/2004</t>
+          <t>25/01/1967</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>3.JOVEN</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>AFILIACION MASIVA DE OFICIO</t>
+          <t>AFILIACION PPDD</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8802,7 +8802,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21011829</t>
+          <t>20412006</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8812,12 +8812,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DE HUAYCAÑE</t>
+          <t>DE ORELLANA</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>HERLINDA AURELIA</t>
+          <t>FORTUNATA</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8826,16 +8826,16 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>25/01/1967</t>
+          <t>07/06/1959</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.ADULTO</t>
+          <t>5.ADULTO MAYOR</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>30/09/2014</t>
+          <t>11/02/2013</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8865,7 +8865,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>20412006</t>
+          <t>76683959</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8875,30 +8875,30 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DE ORELLANA</t>
+          <t>VILLANUEVA</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>FORTUNATA</t>
+          <t>SATURNINO HENRY</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>07/06/1959</t>
+          <t>13/09/1994</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>5.ADULTO MAYOR</t>
+          <t>4.ADULTO</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>11/02/2013</t>
+          <t>30/09/2014</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8928,22 +8928,22 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>76683959</t>
+          <t>76648032</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>YUPANQUI</t>
+          <t>ZARZOSA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VILLANUEVA</t>
+          <t>CHAMORRO</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>SATURNINO HENRY</t>
+          <t>JAVIER ALEX</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>13/09/1994</t>
+          <t>24/06/1994</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8985,69 +8985,6 @@
         </is>
       </c>
       <c r="M136" t="n">
-        <v>120605</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>76648032</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>ZARZOSA</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>CHAMORRO</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>JAVIER ALEX</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="F137" t="n">
-        <v>32</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>24/06/1994</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>4.ADULTO</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>AFILIACION PPDD</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>PEAS MAS PLANES COMPLEMENTARIOS</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>30/09/2014</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>PAMPA HERMOSA</t>
-        </is>
-      </c>
-      <c r="M137" t="n">
         <v>120605</v>
       </c>
     </row>
